--- a/artfynd/A 57522-2025 artfynd.xlsx
+++ b/artfynd/A 57522-2025 artfynd.xlsx
@@ -2230,7 +2230,7 @@
         <v>129688211</v>
       </c>
       <c r="B16" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>129688654</v>
       </c>
       <c r="B17" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>129688219</v>
       </c>
       <c r="B18" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>129688638</v>
       </c>
       <c r="B19" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>129688637</v>
       </c>
       <c r="B20" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>129688220</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>129688639</v>
       </c>
       <c r="B22" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>129688635</v>
       </c>
       <c r="B23" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>129688212</v>
       </c>
       <c r="B24" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>129688636</v>
       </c>
       <c r="B25" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>129688218</v>
       </c>
       <c r="B26" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>129688213</v>
       </c>
       <c r="B27" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 57522-2025 artfynd.xlsx
+++ b/artfynd/A 57522-2025 artfynd.xlsx
@@ -2651,32 +2651,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129688637</v>
+        <v>129688220</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>792976</v>
+        <v>792382</v>
       </c>
       <c r="R20" t="n">
-        <v>7304789</v>
+        <v>7304387</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,12 +2720,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2757,32 +2757,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129688220</v>
+        <v>129688637</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>792382</v>
+        <v>792976</v>
       </c>
       <c r="R21" t="n">
-        <v>7304387</v>
+        <v>7304789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">

--- a/artfynd/A 57522-2025 artfynd.xlsx
+++ b/artfynd/A 57522-2025 artfynd.xlsx
@@ -2969,7 +2969,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129688635</v>
+        <v>129688212</v>
       </c>
       <c r="B23" t="n">
         <v>98774</v>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>793051</v>
+        <v>792776</v>
       </c>
       <c r="R23" t="n">
-        <v>7304501</v>
+        <v>7304623</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3075,7 +3075,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129688212</v>
+        <v>129688635</v>
       </c>
       <c r="B24" t="n">
         <v>98774</v>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>792776</v>
+        <v>793051</v>
       </c>
       <c r="R24" t="n">
-        <v>7304623</v>
+        <v>7304501</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,12 +3144,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3287,7 +3287,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129688218</v>
+        <v>129688213</v>
       </c>
       <c r="B26" t="n">
         <v>98774</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>792638</v>
+        <v>792698</v>
       </c>
       <c r="R26" t="n">
-        <v>7304391</v>
+        <v>7304649</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3393,7 +3393,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129688213</v>
+        <v>129688218</v>
       </c>
       <c r="B27" t="n">
         <v>98774</v>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>792698</v>
+        <v>792638</v>
       </c>
       <c r="R27" t="n">
-        <v>7304649</v>
+        <v>7304391</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 57522-2025 artfynd.xlsx
+++ b/artfynd/A 57522-2025 artfynd.xlsx
@@ -2651,32 +2651,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129688220</v>
+        <v>129688637</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>792382</v>
+        <v>792976</v>
       </c>
       <c r="R20" t="n">
-        <v>7304387</v>
+        <v>7304789</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,12 +2720,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2757,32 +2757,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129688637</v>
+        <v>129688220</v>
       </c>
       <c r="B21" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>792976</v>
+        <v>792382</v>
       </c>
       <c r="R21" t="n">
-        <v>7304789</v>
+        <v>7304387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2969,7 +2969,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129688212</v>
+        <v>129688635</v>
       </c>
       <c r="B23" t="n">
         <v>98774</v>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>792776</v>
+        <v>793051</v>
       </c>
       <c r="R23" t="n">
-        <v>7304623</v>
+        <v>7304501</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3075,7 +3075,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129688635</v>
+        <v>129688212</v>
       </c>
       <c r="B24" t="n">
         <v>98774</v>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>793051</v>
+        <v>792776</v>
       </c>
       <c r="R24" t="n">
-        <v>7304501</v>
+        <v>7304623</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,12 +3144,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3287,7 +3287,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129688213</v>
+        <v>129688218</v>
       </c>
       <c r="B26" t="n">
         <v>98774</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>792698</v>
+        <v>792638</v>
       </c>
       <c r="R26" t="n">
-        <v>7304649</v>
+        <v>7304391</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3393,7 +3393,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129688218</v>
+        <v>129688213</v>
       </c>
       <c r="B27" t="n">
         <v>98774</v>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>792638</v>
+        <v>792698</v>
       </c>
       <c r="R27" t="n">
-        <v>7304391</v>
+        <v>7304649</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 57522-2025 artfynd.xlsx
+++ b/artfynd/A 57522-2025 artfynd.xlsx
@@ -2230,7 +2230,7 @@
         <v>129688211</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>129688654</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>129688219</v>
       </c>
       <c r="B18" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>129688638</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,32 +2651,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129688637</v>
+        <v>129688220</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>792976</v>
+        <v>792382</v>
       </c>
       <c r="R20" t="n">
-        <v>7304789</v>
+        <v>7304387</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,12 +2720,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2757,32 +2757,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129688220</v>
+        <v>129688637</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>792382</v>
+        <v>792976</v>
       </c>
       <c r="R21" t="n">
-        <v>7304387</v>
+        <v>7304789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2866,7 +2866,7 @@
         <v>129688639</v>
       </c>
       <c r="B22" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>129688635</v>
       </c>
       <c r="B23" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>129688212</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>129688636</v>
       </c>
       <c r="B25" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>129688218</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>129688213</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 57522-2025 artfynd.xlsx
+++ b/artfynd/A 57522-2025 artfynd.xlsx
@@ -2230,7 +2230,7 @@
         <v>129688211</v>
       </c>
       <c r="B16" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>129688654</v>
       </c>
       <c r="B17" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>129688219</v>
       </c>
       <c r="B18" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>129688638</v>
       </c>
       <c r="B19" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>129688637</v>
       </c>
       <c r="B21" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>129688639</v>
       </c>
       <c r="B22" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>129688635</v>
       </c>
       <c r="B23" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>129688212</v>
       </c>
       <c r="B24" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>129688636</v>
       </c>
       <c r="B25" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>129688218</v>
       </c>
       <c r="B26" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>129688213</v>
       </c>
       <c r="B27" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 57522-2025 artfynd.xlsx
+++ b/artfynd/A 57522-2025 artfynd.xlsx
@@ -2651,32 +2651,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129688220</v>
+        <v>129688637</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>792382</v>
+        <v>792976</v>
       </c>
       <c r="R20" t="n">
-        <v>7304387</v>
+        <v>7304789</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,12 +2720,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2757,32 +2757,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129688637</v>
+        <v>129688220</v>
       </c>
       <c r="B21" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>792976</v>
+        <v>792382</v>
       </c>
       <c r="R21" t="n">
-        <v>7304789</v>
+        <v>7304387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">

--- a/artfynd/A 57522-2025 artfynd.xlsx
+++ b/artfynd/A 57522-2025 artfynd.xlsx
@@ -2230,7 +2230,7 @@
         <v>129688211</v>
       </c>
       <c r="B16" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>129688654</v>
       </c>
       <c r="B17" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>129688638</v>
       </c>
       <c r="B19" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,32 +2651,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129688637</v>
+        <v>129688220</v>
       </c>
       <c r="B20" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>792976</v>
+        <v>792382</v>
       </c>
       <c r="R20" t="n">
-        <v>7304789</v>
+        <v>7304387</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,12 +2720,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2757,32 +2757,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129688220</v>
+        <v>129688637</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>792382</v>
+        <v>792976</v>
       </c>
       <c r="R21" t="n">
-        <v>7304387</v>
+        <v>7304789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2866,7 +2866,7 @@
         <v>129688639</v>
       </c>
       <c r="B22" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>129688635</v>
       </c>
       <c r="B23" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>129688212</v>
       </c>
       <c r="B24" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>129688636</v>
       </c>
       <c r="B25" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>129688218</v>
       </c>
       <c r="B26" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>129688213</v>
       </c>
       <c r="B27" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 57522-2025 artfynd.xlsx
+++ b/artfynd/A 57522-2025 artfynd.xlsx
@@ -2230,7 +2230,7 @@
         <v>129688211</v>
       </c>
       <c r="B16" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>129688654</v>
       </c>
       <c r="B17" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>129688219</v>
       </c>
       <c r="B18" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>129688638</v>
       </c>
       <c r="B19" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,32 +2651,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129688220</v>
+        <v>129688637</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>98794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>792382</v>
+        <v>792976</v>
       </c>
       <c r="R20" t="n">
-        <v>7304387</v>
+        <v>7304789</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,12 +2720,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2757,32 +2757,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129688637</v>
+        <v>129688220</v>
       </c>
       <c r="B21" t="n">
-        <v>98790</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>792976</v>
+        <v>792382</v>
       </c>
       <c r="R21" t="n">
-        <v>7304789</v>
+        <v>7304387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2866,7 +2866,7 @@
         <v>129688639</v>
       </c>
       <c r="B22" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>129688635</v>
       </c>
       <c r="B23" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>129688212</v>
       </c>
       <c r="B24" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>129688636</v>
       </c>
       <c r="B25" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>129688218</v>
       </c>
       <c r="B26" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>129688213</v>
       </c>
       <c r="B27" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 57522-2025 artfynd.xlsx
+++ b/artfynd/A 57522-2025 artfynd.xlsx
@@ -2230,7 +2230,7 @@
         <v>129688211</v>
       </c>
       <c r="B16" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>129688654</v>
       </c>
       <c r="B17" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>129688219</v>
       </c>
       <c r="B18" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>129688638</v>
       </c>
       <c r="B19" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>129688637</v>
       </c>
       <c r="B20" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>129688220</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>129688639</v>
       </c>
       <c r="B22" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>129688635</v>
       </c>
       <c r="B23" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>129688212</v>
       </c>
       <c r="B24" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>129688636</v>
       </c>
       <c r="B25" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3287,10 +3287,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129688218</v>
+        <v>129688213</v>
       </c>
       <c r="B26" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>792638</v>
+        <v>792698</v>
       </c>
       <c r="R26" t="n">
-        <v>7304391</v>
+        <v>7304649</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129688213</v>
+        <v>129688218</v>
       </c>
       <c r="B27" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>792698</v>
+        <v>792638</v>
       </c>
       <c r="R27" t="n">
-        <v>7304649</v>
+        <v>7304391</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 57522-2025 artfynd.xlsx
+++ b/artfynd/A 57522-2025 artfynd.xlsx
@@ -3287,7 +3287,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129688213</v>
+        <v>129688218</v>
       </c>
       <c r="B26" t="n">
         <v>98797</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>792698</v>
+        <v>792638</v>
       </c>
       <c r="R26" t="n">
-        <v>7304649</v>
+        <v>7304391</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3393,7 +3393,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129688218</v>
+        <v>129688213</v>
       </c>
       <c r="B27" t="n">
         <v>98797</v>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>792638</v>
+        <v>792698</v>
       </c>
       <c r="R27" t="n">
-        <v>7304391</v>
+        <v>7304649</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 57522-2025 artfynd.xlsx
+++ b/artfynd/A 57522-2025 artfynd.xlsx
@@ -2651,32 +2651,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129688637</v>
+        <v>129688220</v>
       </c>
       <c r="B20" t="n">
-        <v>98797</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>792976</v>
+        <v>792382</v>
       </c>
       <c r="R20" t="n">
-        <v>7304789</v>
+        <v>7304387</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,12 +2720,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2757,32 +2757,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129688220</v>
+        <v>129688637</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>98797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>792382</v>
+        <v>792976</v>
       </c>
       <c r="R21" t="n">
-        <v>7304387</v>
+        <v>7304789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3287,7 +3287,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129688218</v>
+        <v>129688213</v>
       </c>
       <c r="B26" t="n">
         <v>98797</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>792638</v>
+        <v>792698</v>
       </c>
       <c r="R26" t="n">
-        <v>7304391</v>
+        <v>7304649</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3393,7 +3393,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129688213</v>
+        <v>129688218</v>
       </c>
       <c r="B27" t="n">
         <v>98797</v>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>792698</v>
+        <v>792638</v>
       </c>
       <c r="R27" t="n">
-        <v>7304649</v>
+        <v>7304391</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 57522-2025 artfynd.xlsx
+++ b/artfynd/A 57522-2025 artfynd.xlsx
@@ -2230,7 +2230,7 @@
         <v>129688211</v>
       </c>
       <c r="B16" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>129688654</v>
       </c>
       <c r="B17" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>129688219</v>
       </c>
       <c r="B18" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>129688638</v>
       </c>
       <c r="B19" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>129688220</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>129688637</v>
       </c>
       <c r="B21" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>129688639</v>
       </c>
       <c r="B22" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>129688635</v>
       </c>
       <c r="B23" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>129688212</v>
       </c>
       <c r="B24" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>129688636</v>
       </c>
       <c r="B25" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3287,10 +3287,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129688213</v>
+        <v>129688218</v>
       </c>
       <c r="B26" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>792698</v>
+        <v>792638</v>
       </c>
       <c r="R26" t="n">
-        <v>7304649</v>
+        <v>7304391</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129688218</v>
+        <v>129688213</v>
       </c>
       <c r="B27" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>792638</v>
+        <v>792698</v>
       </c>
       <c r="R27" t="n">
-        <v>7304391</v>
+        <v>7304649</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 57522-2025 artfynd.xlsx
+++ b/artfynd/A 57522-2025 artfynd.xlsx
@@ -2651,32 +2651,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129688220</v>
+        <v>129688637</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>98798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>792382</v>
+        <v>792976</v>
       </c>
       <c r="R20" t="n">
-        <v>7304387</v>
+        <v>7304789</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,12 +2720,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2757,32 +2757,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129688637</v>
+        <v>129688220</v>
       </c>
       <c r="B21" t="n">
-        <v>98798</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>792976</v>
+        <v>792382</v>
       </c>
       <c r="R21" t="n">
-        <v>7304789</v>
+        <v>7304387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">

--- a/artfynd/A 57522-2025 artfynd.xlsx
+++ b/artfynd/A 57522-2025 artfynd.xlsx
@@ -2230,7 +2230,7 @@
         <v>129688211</v>
       </c>
       <c r="B16" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>129688654</v>
       </c>
       <c r="B17" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>129688219</v>
       </c>
       <c r="B18" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>129688638</v>
       </c>
       <c r="B19" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,32 +2651,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129688637</v>
+        <v>129688220</v>
       </c>
       <c r="B20" t="n">
-        <v>98798</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>792976</v>
+        <v>792382</v>
       </c>
       <c r="R20" t="n">
-        <v>7304789</v>
+        <v>7304387</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,12 +2720,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2757,32 +2757,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129688220</v>
+        <v>129688637</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>98815</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>792382</v>
+        <v>792976</v>
       </c>
       <c r="R21" t="n">
-        <v>7304387</v>
+        <v>7304789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2866,7 +2866,7 @@
         <v>129688639</v>
       </c>
       <c r="B22" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>129688635</v>
       </c>
       <c r="B23" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>129688212</v>
       </c>
       <c r="B24" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>129688636</v>
       </c>
       <c r="B25" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3287,10 +3287,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129688218</v>
+        <v>129688213</v>
       </c>
       <c r="B26" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>792638</v>
+        <v>792698</v>
       </c>
       <c r="R26" t="n">
-        <v>7304391</v>
+        <v>7304649</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129688213</v>
+        <v>129688218</v>
       </c>
       <c r="B27" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>792698</v>
+        <v>792638</v>
       </c>
       <c r="R27" t="n">
-        <v>7304649</v>
+        <v>7304391</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
